--- a/tame_output/ON/bt/strategyON_20240317.xlsx
+++ b/tame_output/ON/bt/strategyON_20240317.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,11 +969,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>475.6%</t>
+          <t>474.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-301.2%</t>
+          <t>-301.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.3%</t>
+          <t>-117.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,27 +1308,27 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-198.5%</t>
+          <t>-191.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-81.7%</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-46.0%</t>
         </is>
       </c>
     </row>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910626</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.618426109584465</v>
+        <v>-6.845637738951424</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.509553923763999</v>
+        <v>0.4186692720172154</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.9792850735290801</v>
+        <v>-1.206496702896039</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.569709747794084</v>
+        <v>2.433382770173909</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.538053754120535</v>
+        <v>-6.765265383487494</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.5562580866970874</v>
+        <v>0.4653734349503038</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.8989127180651505</v>
+        <v>-1.12612434743211</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.632488381819959</v>
+        <v>2.496161404199783</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.505121884307684</v>
+        <v>-6.732333513674643</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.5622116697206319</v>
+        <v>0.4713270179738482</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.8989127180651505</v>
+        <v>-1.12612434743211</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.625269216918363</v>
+        <v>2.488942239298187</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.525286525857231</v>
+        <v>-6.75249815522419</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.5474736223268368</v>
+        <v>0.4565889705800532</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.9190773596146978</v>
+        <v>-1.146288988981657</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.606498241214658</v>
+        <v>2.470171263594483</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.466619595835698</v>
+        <v>-6.693831225202657</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.5720561841740066</v>
+        <v>0.481171532427223</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.8341178911845601</v>
+        <v>-1.061329520551519</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.658589712111297</v>
+        <v>2.522262734491122</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.403550363529359</v>
+        <v>-6.630761992896318</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.5999776057256567</v>
+        <v>0.5090929539788731</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.8626314538667946</v>
+        <v>-1.089843083233754</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.644175303131071</v>
+        <v>2.507848325510896</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.351534849560546</v>
+        <v>-6.578746478927505</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.6247741469995827</v>
+        <v>0.5338894952527991</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.8626314538667946</v>
+        <v>-1.089843083233754</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.648165638817472</v>
+        <v>2.511838661197296</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.175965180639643</v>
+        <v>-6.403176810006602</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.6935267876692022</v>
+        <v>0.6026421359224186</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.8626314538667946</v>
+        <v>-1.089843083233754</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.64669041191873</v>
+        <v>2.510363434298555</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-5.978695774911644</v>
+        <v>-6.205907404278603</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.787487960125274</v>
+        <v>0.6966033083784904</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.6653620481387965</v>
+        <v>-0.8925736775057557</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.780105465520401</v>
+        <v>2.643778487900226</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.779543667674545</v>
+        <v>-6.006755297041504</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.8540976693734308</v>
+        <v>0.7632130176266472</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.5000395221889832</v>
+        <v>-0.7272511515559423</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.866247847443606</v>
+        <v>2.729920869823431</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.553698514955134</v>
+        <v>-5.780910144322093</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.9540148034974036</v>
+        <v>0.86313015175062</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.4581128466018195</v>
+        <v>-0.6853244759687787</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.900982925832113</v>
+        <v>2.764655948211938</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-5.26742370263244</v>
+        <v>-5.494635331999399</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.06966387298254</v>
+        <v>0.9787792212357567</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.4581128466018195</v>
+        <v>-0.6853244759687787</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.902122070388172</v>
+        <v>2.765795092767997</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.040627875559107</v>
+        <v>-5.267839504926066</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.163015977973981</v>
+        <v>1.072131326227197</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.389998901980275</v>
+        <v>-0.6172105313472341</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.945624211323207</v>
+        <v>2.809297233703031</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.756719144630358</v>
+        <v>-4.983930773997317</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.282313174584117</v>
+        <v>1.191428522837334</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.389998901980275</v>
+        <v>-0.6172105313472341</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.951357915561843</v>
+        <v>2.815030937941668</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.509731894437405</v>
+        <v>-4.736943523804364</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.371370812267433</v>
+        <v>1.280486160520649</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.1430116517873229</v>
+        <v>-0.370223281154282</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.089813003283749</v>
+        <v>2.953486025663573</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.245895027233336</v>
+        <v>-4.473106656600295</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.467022077836153</v>
+        <v>1.37613742608937</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.1430116517873229</v>
+        <v>-0.370223281154282</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.079929521970842</v>
+        <v>2.943602544350666</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-3.97865322636494</v>
+        <v>-4.205864855731899</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.572084237684138</v>
+        <v>1.481199585937354</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.1430116517873229</v>
+        <v>-0.370223281154282</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.078094961471468</v>
+        <v>2.941767983851292</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.702844062964456</v>
+        <v>-3.930055692331415</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.682107588070871</v>
+        <v>1.591222936324087</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.05399234350858939</v>
+        <v>-0.2812039728755485</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.131206231465247</v>
+        <v>2.994879253845072</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.433776475197476</v>
+        <v>-3.660988104564435</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.790403129323156</v>
+        <v>1.699518477576373</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.21507524425839</v>
+        <v>-0.01213638510856918</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.293315290270928</v>
+        <v>3.156988312650753</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.16971653687468</v>
+        <v>-3.396928166241639</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.882766788490523</v>
+        <v>1.791882136743739</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.4791351825811861</v>
+        <v>0.251923553214227</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.438490937102854</v>
+        <v>3.302163959482678</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.462636913369842</v>
+        <v>-2.689848542736801</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.162811604232157</v>
+        <v>2.071926952485373</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.4791351825811861</v>
+        <v>0.251923553214227</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.435703903442553</v>
+        <v>3.299376925822378</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.212995883383891</v>
+        <v>-2.44020751275085</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.263011640114379</v>
+        <v>2.172126988367595</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.7287762125671379</v>
+        <v>0.5015645832001787</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.585832145321965</v>
+        <v>3.44950516770179</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.958453984042815</v>
+        <v>-2.185665613409774</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.364195221071566</v>
+        <v>2.273310569324782</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.9833181119082134</v>
+        <v>0.7561064825412542</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.737924106147368</v>
+        <v>3.601597128527192</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.724972761813217</v>
+        <v>-1.952184391180176</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.465512138801258</v>
+        <v>2.374627487054474</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.216799334137812</v>
+        <v>0.9895877047708528</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.885937268322979</v>
+        <v>3.749610290702804</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.545264231669344</v>
+        <v>-1.772475861036303</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.534503340545847</v>
+        <v>2.443618688799064</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.273970838300508</v>
+        <v>1.046759208933549</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.917347960507637</v>
+        <v>3.781020982887462</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.549822674810132</v>
+        <v>3.439568162061807</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-1.396397841782063</v>
+        <v>-1.400166020537004</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.589417383247787</v>
+        <v>2.587910111745811</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.422837228187789</v>
+        <v>1.419069049432848</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.002035281187033</v>
+        <v>3.999774373934068</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240317.xlsx
+++ b/tame_output/ON/bt/strategyON_20240317.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>474.1%</t>
+          <t>473.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-301.6%</t>
+          <t>-325.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.4%</t>
+          <t>-127.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-106.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-46.0%</t>
+          <t>-60.4%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611694</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199884</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910626</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410713</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085275</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081563</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255781</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.439568162061807</v>
+        <v>3.439568162061808</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-1.400166020537004</v>
+        <v>-1.640200387405417</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.587910111745811</v>
+        <v>2.491896364998446</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.419069049432848</v>
+        <v>1.179034682564436</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.999774373934068</v>
+        <v>3.855753753813021</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240317.xlsx
+++ b/tame_output/ON/bt/strategyON_20240317.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-24.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-60.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>111.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-419.0%</t>
+          <t>-449.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-54.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>473.3%</t>
+          <t>494.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-325.6%</t>
+          <t>-356.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-168.0%</t>
+          <t>-180.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-127.0%</t>
+          <t>-139.4%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-223.4%</t>
+          <t>-227.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-191.3%</t>
+          <t>-197.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-106.1%</t>
+          <t>-110.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-134.4%</t>
+          <t>-137.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-60.4%</t>
+          <t>-159.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1905"/>
+  <dimension ref="A1:G1906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.5492738353104052</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.357528887948369</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.881174505190975</v>
+        <v>1.837029514356341</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.26688048125254</v>
+        <v>4.24039348675176</v>
       </c>
     </row>
     <row r="1836">
@@ -43773,22 +43773,22 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355687</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.4435869473681055</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.295079405398897</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.866613431488292</v>
+        <v>1.822468440653658</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.237969109658377</v>
+        <v>4.211482115157597</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.4494363284833499</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.297908296570869</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.866613431488292</v>
+        <v>1.822468440653658</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.238458248384251</v>
+        <v>4.211971253883471</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.4012140616362663</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.282699372453702</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.774246173806574</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.187117876396887</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.7178531474721273</v>
+        <v>0.4090493234731506</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.444296091285588</v>
+        <v>3.320774561685997</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.774246173806574</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.222058960894429</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.7228907381997138</v>
+        <v>0.4140869142007372</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.444888567761961</v>
+        <v>3.32136703816237</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.829890630072891</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.254023074839558</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.6664211070234171</v>
+        <v>0.3576172830244404</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.401047096915179</v>
+        <v>3.277525567315589</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.773420998896595</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.198887677757517</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.6006537169740049</v>
+        <v>0.2918498929750283</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.375757750025884</v>
+        <v>3.252236220426294</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.773420998896595</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.199905286887986</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.5871182331972953</v>
+        <v>0.2783144091983187</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.360971588502956</v>
+        <v>3.237450058903366</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.773420998896595</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.190533318875742</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.5053463327695435</v>
+        <v>0.1965425087705671</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.318345554287094</v>
+        <v>3.194824024687503</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.800456572302731</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.196837388874663</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.4381372248976659</v>
+        <v>0.1293334008986894</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.296227227972045</v>
+        <v>3.172705698372454</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.800456572302731</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.201602705708365</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.4421286776928561</v>
+        <v>0.1333248536938796</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.295648605209361</v>
+        <v>3.172127075609771</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.804448025097921</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.20182237350472</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>0.290431630648921</v>
+        <v>-0.01837219335005547</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.23289667789685</v>
+        <v>3.10937514829726</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.69689596888862</v>
+        <v>1.652750978053986</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.135218031284202</v>
+        <v>4.108731036783421</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>0.06880969709080353</v>
+        <v>-0.239994126908173</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.144114121072525</v>
+        <v>3.020592591472935</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.659369835201251</v>
+        <v>1.615224844366617</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.112568567670702</v>
+        <v>4.086081573169922</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.1391943612622737</v>
+        <v>-0.4479981852612502</v>
       </c>
       <c r="E1849" t="n">
-        <v>3.06580464228522</v>
+        <v>2.942283112685629</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.659369835201251</v>
+        <v>1.615224844366617</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.117460712224627</v>
+        <v>4.090973717723847</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.409594323971159</v>
+        <v>-0.7183981479701356</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.952726113539654</v>
+        <v>2.829204583940063</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.388969872492366</v>
+        <v>1.344824881657732</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.950302190937284</v>
+        <v>3.923815196436504</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-0.4162292464680892</v>
+        <v>-0.7250330704670658</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.943156443847331</v>
+        <v>2.81963491424774</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.382334949995436</v>
+        <v>1.338189959160802</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.939405536745575</v>
+        <v>3.912918542244795</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-0.7442464681955683</v>
+        <v>-1.053050292194545</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.832287844895107</v>
+        <v>2.708766315295517</v>
       </c>
       <c r="F1852" t="n">
-        <v>1.054317728267957</v>
+        <v>1.010172737433323</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.762933493447856</v>
+        <v>3.736446498947076</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-0.7409097216865966</v>
+        <v>-1.049713545685574</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.841721293907264</v>
+        <v>2.718199764307674</v>
       </c>
       <c r="F1853" t="n">
-        <v>1.057009760686988</v>
+        <v>1.012864769852354</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.772647463307844</v>
+        <v>3.746160468807063</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.107620773353142</v>
+        <v>-1.416424597352119</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.696143265284379</v>
+        <v>2.572621735684788</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.6902987090204425</v>
+        <v>0.6461537181858085</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.553727224351648</v>
+        <v>3.527240229850868</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.108051472401738</v>
+        <v>-1.416855296400715</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.694513524477804</v>
+        <v>2.570991994878213</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.6902987090204425</v>
+        <v>0.6461537181858085</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.552269763164511</v>
+        <v>3.525782768663731</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-1.4517342456284</v>
+        <v>-1.760538069627377</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.558809538641754</v>
+        <v>2.435288009042164</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.5823926569932243</v>
+        <v>0.5382476661585902</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.489295255402797</v>
+        <v>3.462808260902016</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-1.809384595866748</v>
+        <v>-2.118188419865725</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.411855457202673</v>
+        <v>2.288333927603083</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.2247423067548762</v>
+        <v>0.1805973159202421</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.270811103916046</v>
+        <v>3.244324109415266</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-1.816045536088896</v>
+        <v>-2.124849360087873</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.410964007814074</v>
+        <v>2.287442478214483</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.2247423067548762</v>
+        <v>0.1805973159202421</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.272584030616305</v>
+        <v>3.246097036115525</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-2.247851329238684</v>
+        <v>-2.556655153237661</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.224574578021563</v>
+        <v>2.101053048421972</v>
       </c>
       <c r="F1859" t="n">
-        <v>0.08832481031360917</v>
+        <v>0.04417981947897509</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.17706642021895</v>
+        <v>3.150579425718169</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-2.574283858106428</v>
+        <v>-2.883087682105404</v>
       </c>
       <c r="E1860" t="n">
-        <v>2.082286341476556</v>
+        <v>1.958764811876965</v>
       </c>
       <c r="F1860" t="n">
-        <v>0.005856559806460993</v>
+        <v>-0.03828843102817309</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.115870244916751</v>
+        <v>3.089383250415971</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-2.575848009216731</v>
+        <v>-2.884651833215707</v>
       </c>
       <c r="E1861" t="n">
-        <v>2.0802412726884</v>
+        <v>1.956719743088809</v>
       </c>
       <c r="F1861" t="n">
-        <v>0.005856559806460993</v>
+        <v>-0.03828843102817309</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.114450836572717</v>
+        <v>3.087963842071936</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-2.939474254117044</v>
+        <v>-3.24827807811602</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.941278334962517</v>
+        <v>1.817756805362926</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.09236507706066482</v>
+        <v>-0.1365100678952989</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.062005414686682</v>
+        <v>3.035518420185902</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-2.937047189588325</v>
+        <v>-3.245851013587302</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.941503675779836</v>
+        <v>1.817982146180244</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.09269785886781645</v>
+        <v>-0.1368428497024505</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.061060260608223</v>
+        <v>3.034573266107443</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.345635966769004</v>
+        <v>-3.65443979076798</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.776829708922323</v>
+        <v>1.653308179322732</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.545431626883129</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.814668538314575</v>
+        <v>2.788181543813795</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-3.758618450910097</v>
+        <v>-4.067422274909074</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.606822147737346</v>
+        <v>1.483300618137755</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.545431626883129</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.809853970786035</v>
+        <v>2.783366976285255</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.175010325197094</v>
+        <v>-4.483814149196071</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.438259448631425</v>
+        <v>1.314737919031834</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.545431626883129</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.807848021394913</v>
+        <v>2.781361026894133</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-4.551687335726939</v>
+        <v>-4.860491159725916</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.297847335088166</v>
+        <v>1.174325805488575</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.545431626883129</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.818106712063592</v>
+        <v>2.791619717562812</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-4.56540220005205</v>
+        <v>-4.874206024051027</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.288460954503817</v>
+        <v>1.164939424904226</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.545431626883129</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.814206277209287</v>
+        <v>2.787719282708507</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-4.87822699929703</v>
+        <v>-5.187030823296007</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.161735954860826</v>
+        <v>1.038214425261235</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.545431626883129</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.812611197264288</v>
+        <v>2.786124202763508</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-4.883040037762367</v>
+        <v>-5.191843861761344</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.163589715403899</v>
+        <v>1.040068185804308</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.5028332707512807</v>
+        <v>-0.5469782615859148</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.815462192371825</v>
+        <v>2.788975197871044</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-5.316389145872603</v>
+        <v>-5.62519296987158</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.9862237676254013</v>
+        <v>0.8627022380258103</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.5028332707512807</v>
+        <v>-0.5469782615859148</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.811435887837422</v>
+        <v>2.784948893336641</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-5.699390534615234</v>
+        <v>-6.008194358614211</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.8329211108067649</v>
+        <v>0.7093995812071738</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.5028332707512807</v>
+        <v>-0.5469782615859148</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.811333786515838</v>
+        <v>2.784846792015057</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.074375860786511</v>
+        <v>-6.383179684785488</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.685498496309684</v>
+        <v>0.5619769667100929</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8778185969225581</v>
+        <v>-0.9219635877571922</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.588914106784501</v>
+        <v>2.562427112283721</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-6.433906183290513</v>
+        <v>-6.74271000728949</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.5470366706061336</v>
+        <v>0.4235151410065425</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8778185969225581</v>
+        <v>-0.9219635877571922</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.594264410082551</v>
+        <v>2.567777415581771</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-6.760306211955526</v>
+        <v>-7.069110035954503</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.424392679097306</v>
+        <v>0.300871149497715</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.204218625587571</v>
+        <v>-1.248363616422205</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.406340412840721</v>
+        <v>2.379853418339941</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.753830065161966</v>
+        <v>-7.062633889160943</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.4300248884364986</v>
+        <v>0.3065033588369075</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.197742478794011</v>
+        <v>-1.241887469628645</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.413267851538626</v>
+        <v>2.386780857037845</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.750139140205555</v>
+        <v>-7.058942964204531</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.4315012584190634</v>
+        <v>0.3079797288194723</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.197742478794011</v>
+        <v>-1.241887469628645</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.413267851538626</v>
+        <v>2.386780857037845</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.742923787333739</v>
+        <v>-7.051727611332716</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.439900596686432</v>
+        <v>0.3163790670868409</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.12796424350363</v>
+        <v>-1.172109234338264</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.460647989831497</v>
+        <v>2.434160995330717</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.691895941251913</v>
+        <v>-7.000699765250889</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.4647942896035984</v>
+        <v>0.3412727600040073</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.052754905196529</v>
+        <v>-1.096899896031163</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.510256147300194</v>
+        <v>2.483769152799414</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910626</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.845637738951424</v>
+        <v>-7.1544415629504</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.4186692720172154</v>
+        <v>0.2951477424176243</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.206496702896039</v>
+        <v>-1.250641693730673</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.433382770173909</v>
+        <v>2.406895775673128</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.765265383487494</v>
+        <v>-7.07406920748647</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.4653734349503038</v>
+        <v>0.3418519053507127</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.12612434743211</v>
+        <v>-1.170269338266744</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.496161404199783</v>
+        <v>2.469674409699003</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.732333513674643</v>
+        <v>-7.04113733767362</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.4713270179738482</v>
+        <v>0.3478054883742572</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.12612434743211</v>
+        <v>-1.170269338266744</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.488942239298187</v>
+        <v>2.462455244797407</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.75249815522419</v>
+        <v>-7.061301979223167</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.4565889705800532</v>
+        <v>0.3330674409804621</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.146288988981657</v>
+        <v>-1.190433979816291</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.470171263594483</v>
+        <v>2.443684269093702</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.693831225202657</v>
+        <v>-7.002635049201634</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.481171532427223</v>
+        <v>0.3576500028276319</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.061329520551519</v>
+        <v>-1.105474511386153</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.522262734491122</v>
+        <v>2.495775739990341</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.630761992896318</v>
+        <v>-6.939565816895294</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.5090929539788731</v>
+        <v>0.3855714243792825</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.089843083233754</v>
+        <v>-1.133988074068388</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.507848325510896</v>
+        <v>2.481361331010115</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.578746478927505</v>
+        <v>-6.887550302926481</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.5338894952527991</v>
+        <v>0.410367965653208</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.089843083233754</v>
+        <v>-1.133988074068388</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.511838661197296</v>
+        <v>2.485351666696516</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.403176810006602</v>
+        <v>-6.711980634005577</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.6026421359224186</v>
+        <v>0.4791206063228279</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.089843083233754</v>
+        <v>-1.133988074068388</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.510363434298555</v>
+        <v>2.483876439797774</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410712</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-6.205907404278603</v>
+        <v>-6.514711228277579</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.6966033083784904</v>
+        <v>0.5730817787788998</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.8925736775057557</v>
+        <v>-0.9367186683403897</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.643778487900226</v>
+        <v>2.617291493399446</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-6.006755297041504</v>
+        <v>-6.31555912104048</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.7632130176266472</v>
+        <v>0.6396914880270561</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.7272511515559423</v>
+        <v>-0.7713961423905764</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.729920869823431</v>
+        <v>2.70343387532265</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085275</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.780910144322093</v>
+        <v>-6.089713968321069</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.86313015175062</v>
+        <v>0.7396086221510294</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.6853244759687787</v>
+        <v>-0.7294694668034127</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.764655948211938</v>
+        <v>2.738168953711157</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-5.494635331999399</v>
+        <v>-5.803439155998375</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.9787792212357567</v>
+        <v>0.8552576916361661</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.6853244759687787</v>
+        <v>-0.7294694668034127</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.765795092767997</v>
+        <v>2.739308098267216</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.267839504926066</v>
+        <v>-5.576643328925042</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.072131326227197</v>
+        <v>0.9486097966276068</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.6172105313472341</v>
+        <v>-0.6613555221818682</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.809297233703031</v>
+        <v>2.78281023920225</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.983930773997317</v>
+        <v>-5.292734597996293</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.191428522837334</v>
+        <v>1.067906993237743</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.6172105313472341</v>
+        <v>-0.6613555221818682</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.815030937941668</v>
+        <v>2.788543943440887</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.736943523804364</v>
+        <v>-5.04574734780334</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.280486160520649</v>
+        <v>1.156964630921059</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.370223281154282</v>
+        <v>-0.4143682719889161</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.953486025663573</v>
+        <v>2.926999031162793</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.473106656600295</v>
+        <v>-4.781910480599271</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.37613742608937</v>
+        <v>1.252615896489779</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.370223281154282</v>
+        <v>-0.4143682719889161</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.943602544350666</v>
+        <v>2.917115549849886</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.205864855731899</v>
+        <v>-4.514668679730875</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.481199585937354</v>
+        <v>1.357678056337764</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.370223281154282</v>
+        <v>-0.4143682719889161</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.941767983851292</v>
+        <v>2.915280989350512</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.930055692331415</v>
+        <v>-4.238859516330391</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.591222936324087</v>
+        <v>1.467701406724496</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.2812039728755485</v>
+        <v>-0.3253489637101826</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.994879253845072</v>
+        <v>2.968392259344291</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.660988104564435</v>
+        <v>-3.969791928563411</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.699518477576373</v>
+        <v>1.575996947976782</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.01213638510856918</v>
+        <v>-0.05628137594320326</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.156988312650753</v>
+        <v>3.130501318149972</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.396928166241639</v>
+        <v>-3.705731990240615</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.791882136743739</v>
+        <v>1.668360607144148</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.251923553214227</v>
+        <v>0.2077785623795929</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.302163959482678</v>
+        <v>3.275676964981898</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.689848542736801</v>
+        <v>-2.998652366735777</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.071926952485373</v>
+        <v>1.948405422885783</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.251923553214227</v>
+        <v>0.2077785623795929</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.299376925822378</v>
+        <v>3.272889931321597</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.44020751275085</v>
+        <v>-2.749011336749826</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.172126988367595</v>
+        <v>2.048605458768004</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.5015645832001787</v>
+        <v>0.4574195923655446</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.44950516770179</v>
+        <v>3.423018173201009</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-2.185665613409774</v>
+        <v>-2.49446943740875</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.273310569324782</v>
+        <v>2.149789039725192</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.7561064825412542</v>
+        <v>0.7119614917066202</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.601597128527192</v>
+        <v>3.575110134026412</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.952184391180176</v>
+        <v>-2.260988215179152</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.374627487054474</v>
+        <v>2.251105957454883</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.9895877047708528</v>
+        <v>0.9454427139362187</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.749610290702804</v>
+        <v>3.723123296202023</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.772475861036303</v>
+        <v>-2.081279685035279</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.443618688799064</v>
+        <v>2.320097159199473</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.046759208933549</v>
+        <v>1.002614218098915</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.781020982887462</v>
+        <v>3.754533988386682</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,45 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.439568162061808</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-1.640200387405417</v>
+        <v>-1.949004211404392</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.491896364998446</v>
+        <v>2.368374835398855</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.179034682564436</v>
+        <v>1.134889691729801</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.855753753813021</v>
+        <v>3.829266759312241</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="2" t="n">
+        <v>45368</v>
+      </c>
+      <c r="B1906" t="n">
+        <v>3.423968985427537</v>
+      </c>
+      <c r="C1906" t="n">
+        <v>2.87370823515877</v>
+      </c>
+      <c r="D1906" t="n">
+        <v>-1.949004211404392</v>
+      </c>
+      <c r="E1906" t="n">
+        <v>2.368374835398855</v>
+      </c>
+      <c r="F1906" t="n">
+        <v>1.134889691729801</v>
+      </c>
+      <c r="G1906" t="n">
+        <v>2.866772032145138</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240317.xlsx
+++ b/tame_output/ON/bt/strategyON_20240317.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-59.9%</t>
+          <t>-55.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,15 +969,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-445.1%</t>
+          <t>-440.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>491.5%</t>
+          <t>488.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-354.5%</t>
+          <t>-305.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-178.4%</t>
+          <t>-176.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-138.6%</t>
+          <t>-118.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-190.7%</t>
+          <t>-198.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-108.9%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.6%</t>
+          <t>-46.5%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.497129146953905</v>
+        <v>0.540748885010686</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.316985423959091</v>
+        <v>3.334433319181803</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4489068801068214</v>
+        <v>0.4925266181636024</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.301776499841924</v>
+        <v>3.319224395064636</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4567421419437058</v>
+        <v>0.5003618800004868</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.339851689074219</v>
+        <v>3.357299584296932</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4617797326712923</v>
+        <v>0.5053994707280733</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.340444165550592</v>
+        <v>3.357892060773304</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4053101014949955</v>
+        <v>0.4489298395517766</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.296602694703811</v>
+        <v>3.314050589926523</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3395427114455835</v>
+        <v>0.3831624495023645</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.271313347814516</v>
+        <v>3.288761243037228</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3260072276688739</v>
+        <v>0.3696269657256549</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.256527186291588</v>
+        <v>3.2739750815143</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2442353272411222</v>
+        <v>0.2878550652979032</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.213901152075725</v>
+        <v>3.231349047298437</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1770262193692445</v>
+        <v>0.2206459574260256</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.191782825760676</v>
+        <v>3.209230720983389</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1810176721644347</v>
+        <v>0.2246374102212157</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.191204202997993</v>
+        <v>3.208652098220705</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>0.02932062512049965</v>
+        <v>0.0729403631772807</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.128452275685482</v>
+        <v>3.145900170908194</v>
       </c>
       <c r="F1847" t="n">
         <v>1.69689596888862</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.1923013084376178</v>
+        <v>-0.1486815703808368</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.039669718861157</v>
+        <v>3.057117614083869</v>
       </c>
       <c r="F1848" t="n">
         <v>1.659369835201251</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.4003053667906951</v>
+        <v>-0.356685628733914</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.961360240073851</v>
+        <v>2.978808135296564</v>
       </c>
       <c r="F1849" t="n">
         <v>1.659369835201251</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.6707053294995804</v>
+        <v>-0.6270855914427993</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.848281711328285</v>
+        <v>2.865729606550997</v>
       </c>
       <c r="F1850" t="n">
         <v>1.388969872492366</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-0.6773402519965106</v>
+        <v>-0.6337205139397295</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.838712041635962</v>
+        <v>2.856159936858675</v>
       </c>
       <c r="F1851" t="n">
         <v>1.382334949995436</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.00535747372399</v>
+        <v>-0.9617377356672087</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.727843442683739</v>
+        <v>2.745291337906451</v>
       </c>
       <c r="F1852" t="n">
         <v>1.054317728267957</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.002020727215018</v>
+        <v>-0.958400989158237</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.737276891695896</v>
+        <v>2.754724786918608</v>
       </c>
       <c r="F1853" t="n">
         <v>1.057009760686988</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.368731778881564</v>
+        <v>-1.325112040824783</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.59169886307301</v>
+        <v>2.609146758295722</v>
       </c>
       <c r="F1854" t="n">
         <v>0.6902987090204425</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.369162477930159</v>
+        <v>-1.325542739873378</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.590069122266435</v>
+        <v>2.607517017489148</v>
       </c>
       <c r="F1855" t="n">
         <v>0.6902987090204425</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-1.712845251156822</v>
+        <v>-1.669225513100041</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.454365136430386</v>
+        <v>2.471813031653098</v>
       </c>
       <c r="F1856" t="n">
         <v>0.5823926569932243</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.07049560139517</v>
+        <v>-2.026875863338389</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.307411054991304</v>
+        <v>2.324858950214017</v>
       </c>
       <c r="F1857" t="n">
         <v>0.2247423067548762</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.077156541617318</v>
+        <v>-2.033536803560537</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.306519605602705</v>
+        <v>2.323967500825417</v>
       </c>
       <c r="F1858" t="n">
         <v>0.2247423067548762</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-2.508962334767106</v>
+        <v>-2.465342596710324</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.120130175810194</v>
+        <v>2.137578071032907</v>
       </c>
       <c r="F1859" t="n">
         <v>0.08832481031360917</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-2.835394863634849</v>
+        <v>-2.791775125578068</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.977841939265188</v>
+        <v>1.9952898344879</v>
       </c>
       <c r="F1860" t="n">
         <v>0.005856559806460993</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-2.836959014745152</v>
+        <v>-2.793339276688371</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.975796870477032</v>
+        <v>1.993244765699744</v>
       </c>
       <c r="F1861" t="n">
         <v>0.005856559806460993</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.200585259645465</v>
+        <v>-3.156965521588684</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.836833932751148</v>
+        <v>1.85428182797386</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.09236507706066482</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.198158195116747</v>
+        <v>-3.154538457059965</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.837059273568467</v>
+        <v>1.854507168791179</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.09269785886781645</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.606746972297425</v>
+        <v>-3.563127234240644</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.672385306710954</v>
+        <v>1.689833201933667</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.5012866360484949</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.019729456438519</v>
+        <v>-3.976109718381737</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.502377745525977</v>
+        <v>1.51982564074869</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.5012866360484949</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.436121330725516</v>
+        <v>-4.392501592668735</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.333815046420056</v>
+        <v>1.351262941642768</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.5012866360484949</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-4.812798341255361</v>
+        <v>-4.769178603198579</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.193402932876797</v>
+        <v>1.210850828099509</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.5012866360484949</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-4.826513205580472</v>
+        <v>-4.78289346752369</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.184016552292448</v>
+        <v>1.20146444751516</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.5012866360484949</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.139338004825452</v>
+        <v>-5.09571826676867</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.057291552649457</v>
+        <v>1.074739447872169</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.5012866360484949</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.144151043290789</v>
+        <v>-5.100531305234007</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.05914531319253</v>
+        <v>1.076593208415242</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.5028332707512807</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-5.577500151401025</v>
+        <v>-5.533880413344243</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.8817793654140327</v>
+        <v>0.8992272606367449</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.5028332707512807</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-5.960501540143656</v>
+        <v>-5.916881802086874</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.7284767085953963</v>
+        <v>0.7459246038181084</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.5028332707512807</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.335486866314933</v>
+        <v>-6.291867128258152</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.5810540940983153</v>
+        <v>0.5985019893210275</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8778185969225581</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-6.695017188818935</v>
+        <v>-6.651397450762153</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.442592268394765</v>
+        <v>0.4600401636174771</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8778185969225581</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.021417217483948</v>
+        <v>-6.977797479427166</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.319948276885937</v>
+        <v>0.3373961721086496</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.204218625587571</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.014941070690388</v>
+        <v>-6.971321332633607</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.3255804862251299</v>
+        <v>0.3430283814478421</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.197742478794011</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.011250145733976</v>
+        <v>-6.967630407677195</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.3270568562076943</v>
+        <v>0.3445047514304069</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.197742478794011</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.004034792862161</v>
+        <v>-6.960415054805379</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.3354561944750634</v>
+        <v>0.3529040896977755</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.12796424350363</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.953006946780334</v>
+        <v>-6.909387208723553</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.3603498873922297</v>
+        <v>0.3777977826149419</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.052754905196529</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.879537115112886</v>
+        <v>-6.835917377056105</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.4051095215526299</v>
+        <v>0.4225574167753425</v>
       </c>
       <c r="F1880" t="n">
         <v>-0.9792850735290801</v>
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.054696815562484</v>
+        <v>-6.755545021592175</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.3496008621203077</v>
+        <v>0.469261579708431</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.154444773978678</v>
+        <v>-0.8989127180651505</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.479169148271842</v>
+        <v>2.632488381819959</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.021764945749633</v>
+        <v>-6.722613151779324</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.3555544451438521</v>
+        <v>0.4752151627319754</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.154444773978678</v>
+        <v>-0.8989127180651505</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.471949983370246</v>
+        <v>2.625269216918363</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.041929587299181</v>
+        <v>-6.742777793328871</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.3408163977500571</v>
+        <v>0.4604771153381804</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.174609415528225</v>
+        <v>-0.9190773596146978</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.453179007666542</v>
+        <v>2.606498241214658</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371243886058</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.983262657277647</v>
+        <v>-6.684110863307338</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.3653989595972265</v>
+        <v>0.4850596771853501</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.089649947098088</v>
+        <v>-0.8341178911845601</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.505270478563181</v>
+        <v>2.658589712111297</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.920193424971307</v>
+        <v>-6.621041631000998</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.3933203811488775</v>
+        <v>0.5129810987370007</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.118163509780322</v>
+        <v>-0.8626314538667946</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.490856069582954</v>
+        <v>2.644175303131071</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.868177911002495</v>
+        <v>-6.569026117032186</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.418116922422803</v>
+        <v>0.5377776400109262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.118163509780322</v>
+        <v>-0.8626314538667946</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.494846405269356</v>
+        <v>2.648165638817472</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.692608242081591</v>
+        <v>-6.393456448111282</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.4868695630924229</v>
+        <v>0.6065302806805462</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.118163509780322</v>
+        <v>-0.8626314538667946</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.493371178370614</v>
+        <v>2.64669041191873</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410712</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-6.495338836353593</v>
+        <v>-6.196187042383284</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.5808307355484943</v>
+        <v>0.700491453136618</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.9208941040523239</v>
+        <v>-0.6653620481387965</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.626786231972285</v>
+        <v>2.780105465520401</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-6.296186729116494</v>
+        <v>-5.997034935146185</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.6474404447966511</v>
+        <v>0.7671011623847743</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.7555715781025105</v>
+        <v>-0.5000395221889832</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.71292861389549</v>
+        <v>2.866247847443606</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085275</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-6.070341576397083</v>
+        <v>-5.771189782426774</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.7473575789206239</v>
+        <v>0.8670182965087476</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.7136449025153468</v>
+        <v>-0.4581128466018195</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.747663692283997</v>
+        <v>2.900982925832113</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-5.784066764074389</v>
+        <v>-5.48491497010408</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.8630066484057606</v>
+        <v>0.9826673659938843</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.7136449025153468</v>
+        <v>-0.4581128466018195</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.748802836840056</v>
+        <v>2.902122070388172</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.557270937001055</v>
+        <v>-5.258119143030746</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.9563587533972018</v>
+        <v>1.076019470985325</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.6455309578938023</v>
+        <v>-0.389998901980275</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.79230497777509</v>
+        <v>2.945624211323207</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-5.273362206072306</v>
+        <v>-4.974210412101997</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.075655950007338</v>
+        <v>1.195316667595461</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.6455309578938023</v>
+        <v>-0.389998901980275</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.798038682013726</v>
+        <v>2.951357915561843</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-5.026374955879354</v>
+        <v>-4.727223161909045</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.164713587690654</v>
+        <v>1.284374305278777</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.3985437077008502</v>
+        <v>-0.1430116517873229</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.936493769735633</v>
+        <v>3.089813003283749</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.762538088675285</v>
+        <v>-4.463386294704976</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.260364853259374</v>
+        <v>1.380025570847497</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.3985437077008502</v>
+        <v>-0.1430116517873229</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.926610288422725</v>
+        <v>3.079929521970842</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.495296287806888</v>
+        <v>-4.196144493836579</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.365427013107359</v>
+        <v>1.485087730695482</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.3985437077008502</v>
+        <v>-0.1430116517873229</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.924775727923351</v>
+        <v>3.078094961471468</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-4.219487124406404</v>
+        <v>-3.920335330436095</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.475450363494091</v>
+        <v>1.595111081082215</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.3095243994221167</v>
+        <v>-0.05399234350858939</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.977886997917131</v>
+        <v>3.131206231465247</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.950419536639425</v>
+        <v>-3.651267742669116</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.583745904746377</v>
+        <v>1.7034066223345</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.04045681165513737</v>
+        <v>0.21507524425839</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.139996056722812</v>
+        <v>3.293315290270928</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.686359598316629</v>
+        <v>-3.387207804346319</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.676109563913743</v>
+        <v>1.795770281501866</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.2236031266676588</v>
+        <v>0.4791351825811861</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.285171703554737</v>
+        <v>3.438490937102854</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.979279974811791</v>
+        <v>-2.680128180841482</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.956154379655377</v>
+        <v>2.075815097243501</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.2236031266676588</v>
+        <v>0.4791351825811861</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.282384669894436</v>
+        <v>3.435703903442553</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.729638944825839</v>
+        <v>-2.43048715085553</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.0563544155376</v>
+        <v>2.176015133125722</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.4732441566536105</v>
+        <v>0.7287762125671379</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.432512911773849</v>
+        <v>3.585832145321965</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-2.475097045484764</v>
+        <v>-2.175945251514455</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.157537996494787</v>
+        <v>2.27719871408291</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.727786055994686</v>
+        <v>0.9833181119082134</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.584604872599251</v>
+        <v>3.737924106147368</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-2.241615823255165</v>
+        <v>-1.942464029284856</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.258854914224478</v>
+        <v>2.378515631812602</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.9612672782242846</v>
+        <v>1.216799334137812</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.732618034774863</v>
+        <v>3.885937268322979</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-2.061907293111293</v>
+        <v>-1.762755499140984</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.327846115969068</v>
+        <v>2.447506833557191</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.018438782386981</v>
+        <v>1.273970838300508</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.764028726959521</v>
+        <v>3.917347960507637</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-1.929631819480406</v>
+        <v>-1.630480025510097</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.37612379216845</v>
+        <v>2.495784509756573</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.150714256017867</v>
+        <v>1.406246311931395</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.83876149788508</v>
+        <v>3.992080731433196</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.468795635185821</v>
+        <v>3.468795635185825</v>
       </c>
       <c r="C1906" t="n">
-        <v>2.901657109370895</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-1.929631819480406</v>
+        <v>-1.43861513125461</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.37612379216845</v>
+        <v>2.575345528146404</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.150714256017867</v>
+        <v>1.406246311931395</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.894720906357263</v>
+        <v>3.994895792120833</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240317.xlsx
+++ b/tame_output/ON/bt/strategyON_20240317.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-14.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-55.9%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,15 +969,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-440.8%</t>
+          <t>-438.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>488.5%</t>
+          <t>485.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-305.4%</t>
+          <t>-327.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-176.7%</t>
+          <t>-175.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-118.7%</t>
+          <t>-145.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-223.4%</t>
+          <t>-242.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-198.5%</t>
+          <t>-346.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>-102.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-134.4%</t>
+          <t>-146.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-76.1%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.540748885010686</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.334433319181803</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4925266181636024</v>
+        <v>0.5173193045571588</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.319224395064636</v>
+        <v>3.329141469622059</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.625692583563124</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.097985722250817</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.5003618800004868</v>
+        <v>0.5251545663940431</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.357299584296932</v>
+        <v>3.367216658854354</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.625692583563124</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.132926806748359</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.5053994707280733</v>
+        <v>0.5301921571216297</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.357892060773304</v>
+        <v>3.367809135330727</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.681337039829441</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.164890920693487</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4489298395517766</v>
+        <v>0.4737225259453329</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.314050589926523</v>
+        <v>3.323967664483945</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.624867408653144</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.109755523611446</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3831624495023645</v>
+        <v>0.4079551358959209</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.288761243037228</v>
+        <v>3.298678317594651</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.624867408653144</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.110773132741916</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3696269657256549</v>
+        <v>0.3944196521192113</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.2739750815143</v>
+        <v>3.283892156071722</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.624867408653144</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.101401164729672</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2878550652979032</v>
+        <v>0.3126477516914596</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.231349047298437</v>
+        <v>3.24126612185586</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.651902982059281</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.107705234728592</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.2206459574260256</v>
+        <v>0.2454386438195819</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.209230720983389</v>
+        <v>3.219147795540811</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.651902982059281</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.112470551562295</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.2246374102212157</v>
+        <v>0.2494300966147721</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.208652098220705</v>
+        <v>3.218569172778128</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.655894434854471</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.112690219358649</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>0.0729403631772807</v>
+        <v>0.09773304957083706</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.145900170908194</v>
+        <v>3.155817245465617</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.69689596888862</v>
+        <v>1.504197387810536</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.135218031284202</v>
+        <v>4.019598882637351</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.1486815703808368</v>
+        <v>-0.1238888839872804</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.057117614083869</v>
+        <v>3.067034688641292</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.659369835201251</v>
+        <v>1.466671254123167</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.112568567670702</v>
+        <v>3.996949419023852</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.356685628733914</v>
+        <v>-0.3318929423403577</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.978808135296564</v>
+        <v>2.988725209853986</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.659369835201251</v>
+        <v>1.466671254123167</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.117460712224627</v>
+        <v>4.001841563577777</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.6270855914427993</v>
+        <v>-0.6022929050492429</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.865729606550997</v>
+        <v>2.87564668110842</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.388969872492366</v>
+        <v>1.196271291414282</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.950302190937284</v>
+        <v>3.834683042290434</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-0.6337205139397295</v>
+        <v>-0.6089278275461731</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.856159936858675</v>
+        <v>2.866077011416097</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.382334949995436</v>
+        <v>1.189636368917351</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.939405536745575</v>
+        <v>3.823786388098725</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-0.9617377356672087</v>
+        <v>-0.9369450492736523</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.745291337906451</v>
+        <v>2.755208412463874</v>
       </c>
       <c r="F1852" t="n">
-        <v>1.054317728267957</v>
+        <v>0.8616191471898723</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.762933493447856</v>
+        <v>3.647314344801005</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-0.958400989158237</v>
+        <v>-0.9336083027646807</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.754724786918608</v>
+        <v>2.764641861476031</v>
       </c>
       <c r="F1853" t="n">
-        <v>1.057009760686988</v>
+        <v>0.8643111796089037</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.772647463307844</v>
+        <v>3.657028314660993</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.325112040824783</v>
+        <v>-1.300319354431226</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.609146758295722</v>
+        <v>2.619063832853145</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.6902987090204425</v>
+        <v>0.4976001279423581</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.553727224351648</v>
+        <v>3.438108075704798</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.325542739873378</v>
+        <v>-1.300750053479822</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.607517017489148</v>
+        <v>2.61743409204657</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.6902987090204425</v>
+        <v>0.4976001279423581</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.552269763164511</v>
+        <v>3.436650614517661</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-1.669225513100041</v>
+        <v>-1.644432826706484</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.471813031653098</v>
+        <v>2.481730106210521</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.5823926569932243</v>
+        <v>0.3896940759151399</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.489295255402797</v>
+        <v>3.373676106755946</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.026875863338389</v>
+        <v>-2.002083176944833</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.324858950214017</v>
+        <v>2.33477602477144</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.2247423067548762</v>
+        <v>0.03204372567679176</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.270811103916046</v>
+        <v>3.155191955269195</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.033536803560537</v>
+        <v>-2.008744117166981</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.323967500825417</v>
+        <v>2.33388457538284</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.2247423067548762</v>
+        <v>0.03204372567679176</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.272584030616305</v>
+        <v>3.156964881969455</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-2.465342596710324</v>
+        <v>-2.440549910316768</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.137578071032907</v>
+        <v>2.147495145590329</v>
       </c>
       <c r="F1859" t="n">
-        <v>0.08832481031360917</v>
+        <v>-0.1043737707644752</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.17706642021895</v>
+        <v>3.061447271572099</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-2.791775125578068</v>
+        <v>-2.766982439184512</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.9952898344879</v>
+        <v>2.005206909045323</v>
       </c>
       <c r="F1860" t="n">
-        <v>0.005856559806460993</v>
+        <v>-0.1868420212716234</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.115870244916751</v>
+        <v>3.000251096269901</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-2.793339276688371</v>
+        <v>-2.768546590294815</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.993244765699744</v>
+        <v>2.003161840257166</v>
       </c>
       <c r="F1861" t="n">
-        <v>0.005856559806460993</v>
+        <v>-0.1868420212716234</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.114450836572717</v>
+        <v>2.998831687925866</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.156965521588684</v>
+        <v>-3.132172835195128</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.85428182797386</v>
+        <v>1.864198902531283</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.09236507706066482</v>
+        <v>-0.2850636581387492</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.062005414686682</v>
+        <v>2.946386266039832</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.154538457059965</v>
+        <v>-3.12974577066641</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.854507168791179</v>
+        <v>1.864424243348602</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.09269785886781645</v>
+        <v>-0.2853964399459009</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.061060260608223</v>
+        <v>2.945441111961372</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.563127234240644</v>
+        <v>-3.538334547847088</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.689833201933667</v>
+        <v>1.699750276491089</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.6939852171265792</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.814668538314575</v>
+        <v>2.699049389667724</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-3.976109718381737</v>
+        <v>-3.951317031988181</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.51982564074869</v>
+        <v>1.529742715306112</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.6939852171265792</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.809853970786035</v>
+        <v>2.694234822139185</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.392501592668735</v>
+        <v>-4.367708906275179</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.351262941642768</v>
+        <v>1.361180016200191</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.6939852171265792</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.807848021394913</v>
+        <v>2.692228872748062</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-4.769178603198579</v>
+        <v>-4.744385916805023</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.210850828099509</v>
+        <v>1.220767902656932</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.6939852171265792</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.818106712063592</v>
+        <v>2.702487563416741</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-4.78289346752369</v>
+        <v>-4.758100781130135</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.20146444751516</v>
+        <v>1.211381522072583</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.6939852171265792</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.814206277209287</v>
+        <v>2.698587128562437</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.09571826676867</v>
+        <v>-5.070925580375114</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.074739447872169</v>
+        <v>1.084656522429592</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.5012866360484949</v>
+        <v>-0.6939852171265792</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.812611197264288</v>
+        <v>2.696992048617437</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.100531305234007</v>
+        <v>-5.075738618840451</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.076593208415242</v>
+        <v>1.086510282972665</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.5028332707512807</v>
+        <v>-0.6955318518293651</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.815462192371825</v>
+        <v>2.699843043724974</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-5.533880413344243</v>
+        <v>-5.509087726950687</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.8992272606367449</v>
+        <v>0.9091443351941675</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.5028332707512807</v>
+        <v>-0.6955318518293651</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.811435887837422</v>
+        <v>2.695816739190571</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-5.916881802086874</v>
+        <v>-5.892089115693318</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.7459246038181084</v>
+        <v>0.7558416783755311</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.5028332707512807</v>
+        <v>-0.6955318518293651</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.811333786515838</v>
+        <v>2.695714637868987</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.291867128258152</v>
+        <v>-6.267074441864596</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.5985019893210275</v>
+        <v>0.6084190638784501</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8778185969225581</v>
+        <v>-1.070517178000642</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.588914106784501</v>
+        <v>2.473294958137651</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-6.651397450762153</v>
+        <v>-6.626604764368597</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.4600401636174771</v>
+        <v>0.4699572381748998</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8778185969225581</v>
+        <v>-1.070517178000642</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.594264410082551</v>
+        <v>2.478645261435701</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-6.977797479427166</v>
+        <v>-6.95300479303361</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.3373961721086496</v>
+        <v>0.3473132466660722</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.204218625587571</v>
+        <v>-1.396917206665655</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.406340412840721</v>
+        <v>2.290721264193871</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.971321332633607</v>
+        <v>-6.946528646240051</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.3430283814478421</v>
+        <v>0.3529454560052647</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.197742478794011</v>
+        <v>-1.390441059872096</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.413267851538626</v>
+        <v>2.297648702891775</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.967630407677195</v>
+        <v>-6.942837721283639</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.3445047514304069</v>
+        <v>0.3544218259878296</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.197742478794011</v>
+        <v>-1.390441059872096</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.413267851538626</v>
+        <v>2.297648702891775</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.960415054805379</v>
+        <v>-6.935622368411823</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.3529040896977755</v>
+        <v>0.3628211642551982</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.12796424350363</v>
+        <v>-1.320662824581714</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.460647989831497</v>
+        <v>2.345028841184646</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.909387208723553</v>
+        <v>-6.884594522329997</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.3777977826149419</v>
+        <v>0.3877148571723645</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.052754905196529</v>
+        <v>-1.245453486274613</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.510256147300194</v>
+        <v>2.394636998653343</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.835917377056105</v>
+        <v>-6.811124690662549</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.4225574167753425</v>
+        <v>0.4324744913327652</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.9792850735290801</v>
+        <v>-1.171983654607164</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.569709747794084</v>
+        <v>2.454090599147233</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.755545021592175</v>
+        <v>-6.730752335198619</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.469261579708431</v>
+        <v>0.479178654265854</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.8989127180651505</v>
+        <v>-1.091611299143235</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.632488381819959</v>
+        <v>2.516869233173108</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.722613151779324</v>
+        <v>-6.96344662061311</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.4752151627319754</v>
+        <v>0.3788817751984617</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.8989127180651505</v>
+        <v>-1.091611299143235</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.625269216918363</v>
+        <v>2.509650068271512</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.742777793328871</v>
+        <v>-6.983611262162657</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.4604771153381804</v>
+        <v>0.3641437278046666</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.9190773596146978</v>
+        <v>-1.111775940692782</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.606498241214658</v>
+        <v>2.490879092567807</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.684110863307338</v>
+        <v>-6.924944332141123</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.4850596771853501</v>
+        <v>0.388726289651836</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.8341178911845601</v>
+        <v>-1.026816472262645</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.658589712111297</v>
+        <v>2.542970563464446</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.621041631000998</v>
+        <v>-6.861875099834783</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.5129810987370007</v>
+        <v>0.416647711203487</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.8626314538667946</v>
+        <v>-1.055330034944879</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.644175303131071</v>
+        <v>2.528556154484221</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.569026117032186</v>
+        <v>-6.809859585865971</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.5377776400109262</v>
+        <v>0.4414442524774125</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.8626314538667946</v>
+        <v>-1.055330034944879</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.648165638817472</v>
+        <v>2.532546490170621</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628915</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.393456448111282</v>
+        <v>-6.634289916945067</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.6065302806805462</v>
+        <v>0.5101968931470324</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.8626314538667946</v>
+        <v>-1.055330034944879</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.64669041191873</v>
+        <v>2.53107126327188</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410712</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-6.196187042383284</v>
+        <v>-6.437020511217069</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.700491453136618</v>
+        <v>0.6041580656031038</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.6653620481387965</v>
+        <v>-0.858060629216881</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.780105465520401</v>
+        <v>2.664486316873551</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.997034935146185</v>
+        <v>-6.23786840397997</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.7671011623847743</v>
+        <v>0.6707677748512606</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.5000395221889832</v>
+        <v>-0.6927381032670676</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.866247847443606</v>
+        <v>2.750628698796756</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085275</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.771189782426774</v>
+        <v>-6.012023251260559</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.8670182965087476</v>
+        <v>0.7706849089752335</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.4581128466018195</v>
+        <v>-0.650811427679904</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.900982925832113</v>
+        <v>2.785363777185263</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-5.48491497010408</v>
+        <v>-5.725748438937865</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.9826673659938843</v>
+        <v>0.8863339784603701</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.4581128466018195</v>
+        <v>-0.650811427679904</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.902122070388172</v>
+        <v>2.786502921741322</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.258119143030746</v>
+        <v>-5.498952611864532</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.076019470985325</v>
+        <v>0.9796860834518113</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.389998901980275</v>
+        <v>-0.5826974830583594</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.945624211323207</v>
+        <v>2.830005062676356</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.974210412101997</v>
+        <v>-5.215043880935783</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.195316667595461</v>
+        <v>1.098983280061947</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.389998901980275</v>
+        <v>-0.5826974830583594</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.951357915561843</v>
+        <v>2.835738766914992</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.727223161909045</v>
+        <v>-4.96805663074283</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.284374305278777</v>
+        <v>1.188040917745263</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.1430116517873229</v>
+        <v>-0.3357102328654074</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.089813003283749</v>
+        <v>2.974193854636898</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.463386294704976</v>
+        <v>-4.704219763538761</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.380025570847497</v>
+        <v>1.283692183313983</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.1430116517873229</v>
+        <v>-0.3357102328654074</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.079929521970842</v>
+        <v>2.964310373323991</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.196144493836579</v>
+        <v>-4.436977962670364</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.485087730695482</v>
+        <v>1.388754343161968</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.1430116517873229</v>
+        <v>-0.3357102328654074</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.078094961471468</v>
+        <v>2.962475812824617</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.920335330436095</v>
+        <v>-4.16116879926988</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.595111081082215</v>
+        <v>1.498777693548701</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.05399234350858939</v>
+        <v>-0.2466909245866739</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.131206231465247</v>
+        <v>3.015587082818396</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.651267742669116</v>
+        <v>-3.892101211502901</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.7034066223345</v>
+        <v>1.607073234800986</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.21507524425839</v>
+        <v>0.02237666318030551</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.293315290270928</v>
+        <v>3.177696141624077</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.387207804346319</v>
+        <v>-3.628041273180105</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.795770281501866</v>
+        <v>1.699436893968353</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.4791351825811861</v>
+        <v>0.2864366015031017</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.438490937102854</v>
+        <v>3.322871788456003</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.680128180841482</v>
+        <v>-2.920961649675267</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.075815097243501</v>
+        <v>1.979481709709987</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.4791351825811861</v>
+        <v>0.2864366015031017</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.435703903442553</v>
+        <v>3.320084754795702</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.43048715085553</v>
+        <v>-2.671320619689316</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.176015133125722</v>
+        <v>2.079681745592209</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.7287762125671379</v>
+        <v>0.5360776314890534</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.585832145321965</v>
+        <v>3.470212996675115</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-2.175945251514455</v>
+        <v>-2.41677872034824</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.27719871408291</v>
+        <v>2.180865326549396</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.9833181119082134</v>
+        <v>0.7906195308301289</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.737924106147368</v>
+        <v>3.622304957500517</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.942464029284856</v>
+        <v>-2.183297498118641</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.378515631812602</v>
+        <v>2.282182244279088</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.216799334137812</v>
+        <v>1.024100753059727</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.885937268322979</v>
+        <v>3.770318119676128</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.762755499140984</v>
+        <v>-2.003588967974769</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.447506833557191</v>
+        <v>2.351173446023678</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.273970838300508</v>
+        <v>1.081272257222424</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.917347960507637</v>
+        <v>3.801728811860787</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-1.630480025510097</v>
+        <v>-1.871313494343882</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.495784509756573</v>
+        <v>2.399451122223059</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.406246311931395</v>
+        <v>1.21354773085331</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.992080731433196</v>
+        <v>3.876461582786346</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.468795635185825</v>
+        <v>3.456155828059202</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>2.971143351143507</v>
       </c>
       <c r="D1906" t="n">
-        <v>-1.43861513125461</v>
+        <v>-1.663070939578002</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.575345528146404</v>
+        <v>2.305558550998559</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.406246311931395</v>
+        <v>1.21354773085331</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.994895792120833</v>
+        <v>3.699271989655493</v>
       </c>
     </row>
   </sheetData>
